--- a/工作-大圣牌/战棋/盘丝洞手牌&法强_三界棋命名修正版.xlsx
+++ b/工作-大圣牌/战棋/盘丝洞手牌&法强_三界棋命名修正版.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{3A931E67-4382-4448-BE27-FD1D50848011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48277220-A237-4CBE-85C9-4DE11F7CABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="手牌，法强" sheetId="1" r:id="rId1"/>
     <sheet name="挤爆" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -349,14 +348,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>护盾，当该部将获得属性值时，手牌中的最左侧的部将同样获得对应属性值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾，当该部将获得属性值时，手牌中的最左侧的部将同样获得双倍属性值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>后援&amp;回合更使：使1个友方部署区和1个手牌区的最左侧的部将获得+2/+2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -370,14 +361,6 @@
   </si>
   <si>
     <t>鼓舞：召唤你手牌中的2个最左侧的部将</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>在本回合中使属性增强类的神通额外+1/+1，每当你使用2个盘丝洞部将，提升+1/+1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>在本回合中使属性增强类的神通额外+1/+1，每当你使用2个盘丝洞部将，提升+2/+2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -497,6 +480,22 @@
   </si>
   <si>
     <t>抱卵蛛</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>在本回合中使属性增强类的神通额外+1/+1，每当你使用了3个盘丝洞部将，提升+1/+1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>在本回合中使属性增强类的神通额外+1/+1，每当你使用了3个盘丝洞部将，提升+2/+2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾，当该部将获得属性值时，手牌中的最左侧的部将获得+4/+4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾，当该部将获得属性值时，手牌中的最左侧的部将获得+8/+8</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -818,19 +817,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="T_1_5" displayName="T_1_5" ref="A1:L53" headerRowDxfId="4" dataDxfId="2" totalsRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="T_1_5" displayName="T_1_5" ref="A1:L53" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="0" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ID" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="类型" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="名称" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="特性描述" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="星级" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="品质" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="攻击" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="生命" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="备注" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="列1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="0" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ID" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="类型" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="名称" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="特性描述" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="星级" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="品质" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="攻击" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="生命" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="备注" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="列1" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{E623A5F6-18A1-49DC-A558-28E126003E7D}" name="列2" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1020,7 +1019,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="31.5" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
@@ -1050,10 +1049,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M1" s="18"/>
       <c r="N1" s="18"/>
@@ -1263,7 +1262,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>18</v>
@@ -1309,7 +1308,7 @@
         <v>71</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>20</v>
@@ -1358,7 +1357,7 @@
         <v>76</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F8" s="8">
         <v>2</v>
@@ -1404,7 +1403,7 @@
         <v>76</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F9" s="8">
         <v>2</v>
@@ -1450,7 +1449,7 @@
         <v>77</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F10" s="8">
         <v>2</v>
@@ -1496,7 +1495,7 @@
         <v>77</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F11" s="8">
         <v>2</v>
@@ -1999,10 +1998,10 @@
         <v>71</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F22" s="8">
         <v>4</v>
@@ -2048,7 +2047,7 @@
         <v>83</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F23" s="8">
         <v>4</v>
@@ -2175,7 +2174,7 @@
         <v>85</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F26" s="8">
         <v>5</v>
@@ -2315,7 +2314,7 @@
         <v>86</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F30" s="8">
         <v>6</v>
@@ -2347,10 +2346,10 @@
         <v>71</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F31" s="8">
         <v>6</v>
@@ -2385,7 +2384,7 @@
         <v>87</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="F32" s="8">
         <v>6</v>
@@ -2420,7 +2419,7 @@
         <v>87</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F33" s="8">
         <v>6</v>
@@ -2525,7 +2524,7 @@
         <v>98</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F36" s="8">
         <v>6</v>
@@ -2560,7 +2559,7 @@
         <v>98</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F37" s="8">
         <v>6</v>
@@ -2926,7 +2925,7 @@
         <v>71</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>51</v>
@@ -2958,7 +2957,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>51</v>
@@ -2993,7 +2992,7 @@
         <v>90</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -3025,7 +3024,7 @@
         <v>90</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
@@ -3054,7 +3053,7 @@
         <v>71</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>52</v>
@@ -3086,7 +3085,7 @@
         <v>71</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
@@ -3151,13 +3150,13 @@
         <v>91</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F12" s="8">
         <v>3</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H12" s="8">
         <v>3</v>
@@ -3177,7 +3176,7 @@
         <v>71</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>54</v>
@@ -3209,7 +3208,7 @@
         <v>71</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>55</v>
@@ -3241,7 +3240,7 @@
         <v>71</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>56</v>
@@ -3273,7 +3272,7 @@
         <v>71</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>57</v>
@@ -3305,7 +3304,7 @@
         <v>71</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>53</v>
@@ -3337,7 +3336,7 @@
         <v>71</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8">
@@ -3429,7 +3428,7 @@
         <v>71</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>60</v>
@@ -3617,7 +3616,7 @@
         <v>71</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>64</v>
@@ -3679,7 +3678,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>65</v>
@@ -3711,7 +3710,7 @@
         <v>71</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
@@ -3803,7 +3802,7 @@
         <v>71</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>67</v>
@@ -3835,7 +3834,7 @@
         <v>71</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>68</v>
@@ -3870,7 +3869,7 @@
         <v>96</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F35" s="8">
         <v>6</v>
